--- a/philopoly_trivia_database_template.xlsx
+++ b/philopoly_trivia_database_template.xlsx
@@ -2,19 +2,19 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Command Center" sheetId="1" r:id="R8b848573aaad4929"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Topic Controls" sheetId="2" r:id="R31c7a5c4ffbe4bf0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="3" r:id="R165d132c26904c54"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movies" sheetId="4" r:id="R88f08e4f0fc642ac"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Music" sheetId="5" r:id="Rd343a7aa24c0483a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Family Facts" sheetId="6" r:id="Red2b0e9c5d1b41ec"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Wild Card" sheetId="7" r:id="R2dd7ca1c7a43498a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sports" sheetId="8" r:id="R53a5cfc994134b69"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Geography" sheetId="9" r:id="Rf8ac71d2edbf4544"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="History" sheetId="10" r:id="R38dbf2a25ce949dd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Science" sheetId="11" r:id="R2a69809d46994584"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Food &amp; Drink" sheetId="12" r:id="R8390e91e6d5c4e7d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TV &amp; Pop Culture" sheetId="13" r:id="R16817a4f7917478c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Command Center" sheetId="1" r:id="R276be2ec55644663"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Topic Controls" sheetId="2" r:id="R08ed0868a30c4d8d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="3" r:id="R9d3e36831abd42a6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movies" sheetId="4" r:id="Rd908fda1f1524c13"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Music" sheetId="5" r:id="Re422691c77ef4d32"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Family Facts" sheetId="6" r:id="R1a774c0512704a07"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Wild Card" sheetId="7" r:id="R794f5bf7ea204ec1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sports" sheetId="8" r:id="R84aaa5392b89486b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Geography" sheetId="9" r:id="R59601eb65a58426d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="History" sheetId="10" r:id="R8877c1a6c1f3490b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Science" sheetId="11" r:id="R91c847887ee04402"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Food &amp; Drink" sheetId="12" r:id="Rbe890ecff4f847a3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TV &amp; Pop Culture" sheetId="13" r:id="Rf78b08c530374dd3"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -560,7 +560,7 @@
         <x:v>Game Title</x:v>
       </x:c>
       <x:c r="B5" s="22" t="str">
-        <x:v>Family Trivia Night</x:v>
+        <x:v>Philopoly</x:v>
       </x:c>
       <x:c r="C5" s="23" t="str">
         <x:v>Shown at the top of the game.</x:v>
